--- a/scatter_reg.xlsx
+++ b/scatter_reg.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10209"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/itoudaiki/Dropbox/技術評論社情報Ⅰ問題集原稿/素材/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A34DEE1A-1EF5-1B45-8416-AEE517FB58C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{344677AF-17F3-564A-B663-53DC90C88ADF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="25600" windowHeight="19500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20800" yWindow="1500" windowWidth="25600" windowHeight="19500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="数学テスト結果" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">数学テスト結果!$A$1:$C$11</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -420,10 +423,10 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -431,10 +434,10 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="C3">
-        <v>35</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -442,10 +445,10 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -453,10 +456,10 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="C5">
-        <v>45</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -464,10 +467,10 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="C6">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -475,10 +478,10 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -486,10 +489,10 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="C8">
-        <v>65</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -497,10 +500,10 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="C9">
-        <v>70</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -508,10 +511,10 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C10">
-        <v>75</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -519,13 +522,14 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="C11">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C11" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/scatter_reg.xlsx
+++ b/scatter_reg.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/itoudaiki/Dropbox/技術評論社情報Ⅰ問題集原稿/素材/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{344677AF-17F3-564A-B663-53DC90C88ADF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BBED720-6EA1-3B45-9C39-B5F3BC7834F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20800" yWindow="1500" windowWidth="25600" windowHeight="19500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="27220" yWindow="4540" windowWidth="25600" windowHeight="19500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="数学テスト結果" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,6 @@
   </si>
   <si>
     <t>被験者番号</t>
-    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -423,10 +422,10 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="C2">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -434,10 +433,10 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="C3">
-        <v>70</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -445,10 +444,10 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>8</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="C4">
-        <v>30</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -456,10 +455,10 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>3.5</v>
+        <v>5.6</v>
       </c>
       <c r="C5">
-        <v>80</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -467,10 +466,10 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>5.5</v>
+        <v>6.9</v>
       </c>
       <c r="C6">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -478,10 +477,10 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="C7">
-        <v>65</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -489,10 +488,10 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>6.5</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="C8">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -500,10 +499,10 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>7.5</v>
+        <v>2.9</v>
       </c>
       <c r="C9">
-        <v>35</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -511,10 +510,10 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>6</v>
+        <v>7.3</v>
       </c>
       <c r="C10">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -522,10 +521,10 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>4</v>
+        <v>9.1</v>
       </c>
       <c r="C11">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/scatter_reg.xlsx
+++ b/scatter_reg.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10420"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/itoudaiki/Dropbox/技術評論社情報Ⅰ問題集原稿/素材/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/itoudaiki/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BBED720-6EA1-3B45-9C39-B5F3BC7834F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{014B9D45-33BE-3E46-A8C1-97717FBC7EDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="27220" yWindow="4540" windowWidth="25600" windowHeight="19500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25600" yWindow="2100" windowWidth="25600" windowHeight="19500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="数学テスト結果" sheetId="1" r:id="rId1"/>
@@ -36,15 +36,177 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
-  <si>
-    <t>睡眠時間（時間）</t>
-  </si>
-  <si>
-    <t>ストレスレベル（スコア）</t>
-  </si>
-  <si>
-    <t>被験者番号</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
+  <si>
+    <t>都道府県</t>
+    <rPh sb="0" eb="4">
+      <t xml:space="preserve">トドウフケン </t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>スポーツの年間行動者率（10歳以上）</t>
+    <rPh sb="5" eb="7">
+      <t xml:space="preserve">ネンカン </t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t xml:space="preserve">コウドウシャリツ </t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>一般病院数（人口10万人当たり）</t>
+  </si>
+  <si>
+    <t>１人当たりの国民医療費</t>
+  </si>
+  <si>
+    <t>北海道</t>
+  </si>
+  <si>
+    <t>青森県</t>
+  </si>
+  <si>
+    <t>岩手県</t>
+  </si>
+  <si>
+    <t>宮城県</t>
+  </si>
+  <si>
+    <t>秋田県</t>
+  </si>
+  <si>
+    <t>山形県</t>
+  </si>
+  <si>
+    <t>福島県</t>
+  </si>
+  <si>
+    <t>茨城県</t>
+  </si>
+  <si>
+    <t>栃木県</t>
+  </si>
+  <si>
+    <t>群馬県</t>
+  </si>
+  <si>
+    <t>埼玉県</t>
+  </si>
+  <si>
+    <t>千葉県</t>
+  </si>
+  <si>
+    <t>東京都</t>
+  </si>
+  <si>
+    <t>神奈川県</t>
+  </si>
+  <si>
+    <t>新潟県</t>
+  </si>
+  <si>
+    <t>富山県</t>
+  </si>
+  <si>
+    <t>石川県</t>
+  </si>
+  <si>
+    <t>福井県</t>
+  </si>
+  <si>
+    <t>山梨県</t>
+  </si>
+  <si>
+    <t>長野県</t>
+  </si>
+  <si>
+    <t>岐阜県</t>
+  </si>
+  <si>
+    <t>静岡県</t>
+  </si>
+  <si>
+    <t>愛知県</t>
+  </si>
+  <si>
+    <t>三重県</t>
+  </si>
+  <si>
+    <t>滋賀県</t>
+  </si>
+  <si>
+    <t>京都府</t>
+  </si>
+  <si>
+    <t>大阪府</t>
+  </si>
+  <si>
+    <t>兵庫県</t>
+  </si>
+  <si>
+    <t>奈良県</t>
+  </si>
+  <si>
+    <t>和歌山県</t>
+  </si>
+  <si>
+    <t>鳥取県</t>
+  </si>
+  <si>
+    <t>島根県</t>
+  </si>
+  <si>
+    <t>岡山県</t>
+  </si>
+  <si>
+    <t>広島県</t>
+  </si>
+  <si>
+    <t>山口県</t>
+  </si>
+  <si>
+    <t>徳島県</t>
+  </si>
+  <si>
+    <t>香川県</t>
+  </si>
+  <si>
+    <t>愛媛県</t>
+  </si>
+  <si>
+    <t>高知県</t>
+  </si>
+  <si>
+    <t>福岡県</t>
+  </si>
+  <si>
+    <t>佐賀県</t>
+  </si>
+  <si>
+    <t>長崎県</t>
+  </si>
+  <si>
+    <t>熊本県</t>
+  </si>
+  <si>
+    <t>大分県</t>
+  </si>
+  <si>
+    <t>宮崎県</t>
+  </si>
+  <si>
+    <t>鹿児島県</t>
+  </si>
+  <si>
+    <t>沖縄県</t>
+    <rPh sb="0" eb="2">
+      <t>オキナワ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ケン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -403,128 +565,679 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2">
-        <v>1</v>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
       </c>
       <c r="B2">
-        <v>7.8</v>
+        <v>62.2</v>
       </c>
       <c r="C2">
+        <v>9</v>
+      </c>
+      <c r="D2">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
+        <v>52.1</v>
+      </c>
+      <c r="C3">
+        <v>6.1</v>
+      </c>
+      <c r="D3">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4">
+        <v>59.1</v>
+      </c>
+      <c r="C4">
+        <v>6.5</v>
+      </c>
+      <c r="D4">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5">
+        <v>64.400000000000006</v>
+      </c>
+      <c r="C5">
+        <v>4.7</v>
+      </c>
+      <c r="D5">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>57.1</v>
+      </c>
+      <c r="C6">
+        <v>5.3</v>
+      </c>
+      <c r="D6">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>58.4</v>
+      </c>
+      <c r="C7">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="D7">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
+        <v>59.5</v>
+      </c>
+      <c r="C8">
+        <v>5.6</v>
+      </c>
+      <c r="D8">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9">
+        <v>65.8</v>
+      </c>
+      <c r="C9">
+        <v>5.4</v>
+      </c>
+      <c r="D9">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10">
+        <v>62.6</v>
+      </c>
+      <c r="C10">
+        <v>4.8</v>
+      </c>
+      <c r="D10">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11">
+        <v>67</v>
+      </c>
+      <c r="C11">
+        <v>6</v>
+      </c>
+      <c r="D11">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12">
+        <v>69.3</v>
+      </c>
+      <c r="C12">
+        <v>4</v>
+      </c>
+      <c r="D12">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13">
+        <v>67.400000000000006</v>
+      </c>
+      <c r="C13">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="D13">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14">
+        <v>74.5</v>
+      </c>
+      <c r="C14">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="D14">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15">
+        <v>71.8</v>
+      </c>
+      <c r="C15">
+        <v>3.2</v>
+      </c>
+      <c r="D15">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16">
+        <v>59</v>
+      </c>
+      <c r="C16">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="D16">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17">
+        <v>59.7</v>
+      </c>
+      <c r="C17">
+        <v>8.6</v>
+      </c>
+      <c r="D17">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18">
+        <v>63.4</v>
+      </c>
+      <c r="C18">
+        <v>7</v>
+      </c>
+      <c r="D18">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19">
+        <v>61.5</v>
+      </c>
+      <c r="C19">
+        <v>7.6</v>
+      </c>
+      <c r="D19">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20">
+        <v>62.2</v>
+      </c>
+      <c r="C20">
+        <v>6.5</v>
+      </c>
+      <c r="D20">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21">
+        <v>64</v>
+      </c>
+      <c r="C21">
+        <v>5.4</v>
+      </c>
+      <c r="D21">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22">
+        <v>64.099999999999994</v>
+      </c>
+      <c r="C22">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="D22">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23">
+        <v>66.3</v>
+      </c>
+      <c r="C23">
+        <v>3.9</v>
+      </c>
+      <c r="D23">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24">
+        <v>68.8</v>
+      </c>
+      <c r="C24">
+        <v>3.7</v>
+      </c>
+      <c r="D24">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" t="s">
+        <v>27</v>
+      </c>
+      <c r="B25">
+        <v>64.3</v>
+      </c>
+      <c r="C25">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="D25">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" t="s">
+        <v>28</v>
+      </c>
+      <c r="B26">
+        <v>67.2</v>
+      </c>
+      <c r="C26">
+        <v>3.6</v>
+      </c>
+      <c r="D26">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" t="s">
+        <v>29</v>
+      </c>
+      <c r="B27">
+        <v>67</v>
+      </c>
+      <c r="C27">
+        <v>5.8</v>
+      </c>
+      <c r="D27">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" t="s">
+        <v>30</v>
+      </c>
+      <c r="B28">
+        <v>66.099999999999994</v>
+      </c>
+      <c r="C28">
+        <v>5.3</v>
+      </c>
+      <c r="D28">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" t="s">
+        <v>31</v>
+      </c>
+      <c r="B29">
+        <v>66.400000000000006</v>
+      </c>
+      <c r="C29">
+        <v>5.8</v>
+      </c>
+      <c r="D29">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B30">
+        <v>64.8</v>
+      </c>
+      <c r="C30">
+        <v>5.4</v>
+      </c>
+      <c r="D30">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" t="s">
+        <v>33</v>
+      </c>
+      <c r="B31">
+        <v>59.8</v>
+      </c>
+      <c r="C31">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="D31">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" t="s">
+        <v>34</v>
+      </c>
+      <c r="B32">
+        <v>61.2</v>
+      </c>
+      <c r="C32">
+        <v>7.2</v>
+      </c>
+      <c r="D32">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" t="s">
+        <v>35</v>
+      </c>
+      <c r="B33">
+        <v>61.4</v>
+      </c>
+      <c r="C33">
+        <v>5.6</v>
+      </c>
+      <c r="D33">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" t="s">
+        <v>36</v>
+      </c>
+      <c r="B34">
+        <v>64.8</v>
+      </c>
+      <c r="C34">
+        <v>7.7</v>
+      </c>
+      <c r="D34">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35">
+        <v>65.3</v>
+      </c>
+      <c r="C35">
+        <v>7.3</v>
+      </c>
+      <c r="D35">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>3.5</v>
-      </c>
-      <c r="C3">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="C4">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>5.6</v>
-      </c>
-      <c r="C5">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>6.9</v>
-      </c>
-      <c r="C6">
+      <c r="B36">
+        <v>63.2</v>
+      </c>
+      <c r="C36">
+        <v>8.5</v>
+      </c>
+      <c r="D36">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37">
+        <v>60.9</v>
+      </c>
+      <c r="C37">
+        <v>12.9</v>
+      </c>
+      <c r="D37">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38">
+        <v>61.8</v>
+      </c>
+      <c r="C38">
+        <v>8.1</v>
+      </c>
+      <c r="D38">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39">
+        <v>64</v>
+      </c>
+      <c r="C39">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="D39">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40">
+        <v>59.4</v>
+      </c>
+      <c r="C40">
+        <v>16</v>
+      </c>
+      <c r="D40">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41">
+        <v>67</v>
+      </c>
+      <c r="C41">
+        <v>7.6</v>
+      </c>
+      <c r="D41">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" t="s">
+        <v>44</v>
+      </c>
+      <c r="B42">
+        <v>62.8</v>
+      </c>
+      <c r="C42">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="D42">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" t="s">
+        <v>45</v>
+      </c>
+      <c r="B43">
+        <v>57.8</v>
+      </c>
+      <c r="C43">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="D43">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" t="s">
+        <v>46</v>
+      </c>
+      <c r="B44">
+        <v>66.599999999999994</v>
+      </c>
+      <c r="C44">
+        <v>9.6</v>
+      </c>
+      <c r="D44">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" t="s">
+        <v>47</v>
+      </c>
+      <c r="B45">
+        <v>63.1</v>
+      </c>
+      <c r="C45">
+        <v>11.4</v>
+      </c>
+      <c r="D45">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" t="s">
+        <v>48</v>
+      </c>
+      <c r="B46">
+        <v>65.8</v>
+      </c>
+      <c r="C46">
+        <v>10.9</v>
+      </c>
+      <c r="D46">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" t="s">
+        <v>49</v>
+      </c>
+      <c r="B47">
+        <v>63.5</v>
+      </c>
+      <c r="C47">
+        <v>12.3</v>
+      </c>
+      <c r="D47">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>4.8</v>
-      </c>
-      <c r="C7">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="C8">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9">
-        <v>2.9</v>
-      </c>
-      <c r="C9">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10">
-        <v>7.3</v>
-      </c>
-      <c r="C10">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11">
-        <v>9.1</v>
-      </c>
-      <c r="C11">
-        <v>47</v>
+      <c r="B48">
+        <v>65.8</v>
+      </c>
+      <c r="C48">
+        <v>5.2</v>
+      </c>
+      <c r="D48">
+        <v>334</v>
       </c>
     </row>
   </sheetData>
